--- a/data/trans_dic/P42-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P42-Habitat-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85,62%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>81,19%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,2; 77,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,9; 88,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79,58; 85,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,81; 83,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,15; 77,74</t>
+          <t>71,2; 77,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,62; 87,95</t>
+          <t>82,9; 88,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,39; 85,31</t>
+          <t>79,58; 85,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,5; 83,99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71,15; 77,74</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82,62; 87,95</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79,39; 85,31</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,5; 83,99</t>
+          <t>77,81; 83,85</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>84,56%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75,21; 80,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,5; 86,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,32; 90,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,96; 87,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,27; 80,88</t>
+          <t>75,21; 80,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,23; 87,08</t>
+          <t>82,5; 86,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,44; 90,24</t>
+          <t>86,32; 90,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,6; 86,89</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>75,27; 80,88</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82,23; 87,08</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86,44; 90,24</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>81,6; 86,89</t>
+          <t>81,96; 87,28</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,56%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,48; 86,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,41; 91,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,18; 89,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,14; 91,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,33; 86,01</t>
+          <t>80,48; 86,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 92,12</t>
+          <t>87,41; 91,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,4; 89,35</t>
+          <t>84,18; 89,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 90,86</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80,33; 86,01</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87,89; 92,12</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>84,4; 89,35</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>27,95; 90,86</t>
+          <t>29,14; 91,05</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>80,3%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>83,76%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,62; 82,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,0; 90,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,06; 91,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,62; 87,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,85; 82,75</t>
+          <t>77,62; 82,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,39; 90,4</t>
+          <t>86,0; 90,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,98; 91,12</t>
+          <t>87,06; 91,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,73; 87,97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77,85; 82,75</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86,39; 90,4</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86,98; 91,12</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,73; 87,97</t>
+          <t>80,62; 87,77</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>78,55%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,74; 80,45</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,08; 88,28</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,12; 88,42</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,58; 85,19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>77,74; 80,45</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>86,08; 88,28</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86,12; 88,42</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,58; 85,19</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
     </row>
@@ -1344,16 +1108,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,7 +1128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1378,22 +1141,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,20 +1160,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1455,26 +1206,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1491,10 +1222,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1509,22 +1236,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>512</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1543,26 +1270,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>786</t>
         </is>
@@ -1577,22 +1284,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>509136</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>594315</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1611,26 +1318,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>410800</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>509136</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>594315</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>553405</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>410800</t>
         </is>
@@ -1645,62 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485602; 529690</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>575399; 611405</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>532856; 572247</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>393694; 424299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>485232; 530204</t>
+          <t>485602; 529690</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>573509; 610470</t>
+          <t>575399; 611405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>531555; 571230</t>
+          <t>532856; 572247</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>392147; 424981</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>485232; 530204</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>573509; 610470</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>531555; 571230</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>392147; 424981</t>
+          <t>393694; 424299</t>
         </is>
       </c>
     </row>
@@ -1717,22 +1384,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>702</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>790</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1751,26 +1418,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1036</t>
         </is>
@@ -1785,22 +1432,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>753919</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>870924</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>913510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,26 +1466,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>622026</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>753919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>870924</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>913510</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>622026</t>
         </is>
@@ -1853,62 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>726389; 777689</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>845925; 890995</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>892190; 933272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>602885; 642001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>727032; 781134</t>
+          <t>726389; 777689</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>843186; 892900</t>
+          <t>845925; 890995</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>893477; 932806</t>
+          <t>892190; 933272</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>600198; 639136</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>727032; 781134</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>843186; 892900</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>893477; 932806</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>600198; 639136</t>
+          <t>602885; 642001</t>
         </is>
       </c>
     </row>
@@ -1925,22 +1532,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1959,26 +1566,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
@@ -1993,22 +1580,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>569315</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695469</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>676852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2027,26 +1614,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>471024</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>569315</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>695469</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>676852</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>471024</t>
         </is>
@@ -2061,62 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>550384; 588931</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>675625; 710697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>655517; 694984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>212570; 664289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>549304; 588148</t>
+          <t>550384; 588931</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>679300; 711995</t>
+          <t>675625; 710697</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>657183; 695747</t>
+          <t>655517; 694984</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>203893; 662892</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>549304; 588148</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>679300; 711995</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>657183; 695747</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>203893; 662892</t>
+          <t>212570; 664289</t>
         </is>
       </c>
     </row>
@@ -2133,22 +1680,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>878</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2167,26 +1714,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1019</t>
         </is>
@@ -2201,22 +1728,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>828986</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>922492</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>922787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>716265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2235,26 +1762,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>716265</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>828986</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>922492</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>922787</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>716265</t>
         </is>
@@ -2269,62 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>801296; 852030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>898447; 941685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>901302; 942083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>689422; 750536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>803729; 854342</t>
+          <t>801296; 852030</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>902481; 944458</t>
+          <t>898447; 941685</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>900425; 943260</t>
+          <t>901302; 942083</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>690332; 752214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>803729; 854342</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>902481; 944458</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>900425; 943260</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>690332; 752214</t>
+          <t>689422; 750536</t>
         </is>
       </c>
     </row>
@@ -2341,22 +1828,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2375,26 +1862,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3520</t>
         </is>
@@ -2409,22 +1876,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3083200</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3066554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2220114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2443,26 +1910,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2220114</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3083200</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3066554</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2220114</t>
         </is>
@@ -2477,62 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2615119; 2706419</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3044776; 3122790</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3028943; 3109819</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1683901; 2407647</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2615119; 2706419</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3044776; 3122790</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3028943; 3109819</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1683901; 2407647</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
     </row>
@@ -2544,15 +1971,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P42-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P42-Habitat-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,2; 77,67</t>
+          <t>71,76; 78,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,9; 88,08</t>
+          <t>82,72; 88,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,58; 85,46</t>
+          <t>79,58; 85,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,81; 83,85</t>
+          <t>77,44; 83,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,2; 77,67</t>
+          <t>71,76; 78,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,9; 88,08</t>
+          <t>82,72; 88,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,58; 85,46</t>
+          <t>79,58; 85,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,81; 83,85</t>
+          <t>77,44; 83,8</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,21; 80,52</t>
+          <t>75,15; 80,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,5; 86,89</t>
+          <t>82,46; 87,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,32; 90,29</t>
+          <t>86,06; 90,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,96; 87,28</t>
+          <t>81,65; 87,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,21; 80,52</t>
+          <t>75,15; 80,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,5; 86,89</t>
+          <t>82,46; 87,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,32; 90,29</t>
+          <t>86,06; 90,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,96; 87,28</t>
+          <t>81,65; 87,13</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,48; 86,12</t>
+          <t>80,31; 85,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,41; 91,95</t>
+          <t>87,41; 92,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,18; 89,25</t>
+          <t>84,23; 89,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 91,05</t>
+          <t>85,34; 91,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,48; 86,12</t>
+          <t>80,31; 85,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,41; 91,95</t>
+          <t>87,41; 92,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,18; 89,25</t>
+          <t>84,23; 89,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 91,05</t>
+          <t>85,34; 91,65</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,62; 82,53</t>
+          <t>77,66; 82,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,0; 90,14</t>
+          <t>86,15; 90,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,06; 91,0</t>
+          <t>86,94; 90,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,62; 87,77</t>
+          <t>78,57; 84,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,62; 82,53</t>
+          <t>77,66; 82,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,0; 90,14</t>
+          <t>86,15; 90,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,06; 91,0</t>
+          <t>86,94; 90,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,62; 87,77</t>
+          <t>78,57; 84,22</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410800</t>
+          <t>442874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>410800</t>
+          <t>442874</t>
         </is>
       </c>
     </row>
@@ -1332,42 +1332,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>485602; 529690</t>
+          <t>489402; 532751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>575399; 611405</t>
+          <t>574215; 611940</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>532856; 572247</t>
+          <t>532824; 570541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>393694; 424299</t>
+          <t>424528; 459401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>485602; 529690</t>
+          <t>489402; 532751</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>575399; 611405</t>
+          <t>574215; 611940</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>532856; 572247</t>
+          <t>532824; 570541</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>393694; 424299</t>
+          <t>424528; 459401</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>622026</t>
+          <t>693959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>622026</t>
+          <t>693959</t>
         </is>
       </c>
     </row>
@@ -1480,42 +1480,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>726389; 777689</t>
+          <t>725795; 779901</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>845925; 890995</t>
+          <t>845573; 893115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>892190; 933272</t>
+          <t>889544; 932303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>602885; 642001</t>
+          <t>670249; 715239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>726389; 777689</t>
+          <t>725795; 779901</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>845925; 890995</t>
+          <t>845573; 893115</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>892190; 933272</t>
+          <t>889544; 932303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>602885; 642001</t>
+          <t>670249; 715239</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471024</t>
+          <t>508954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>471024</t>
+          <t>508954</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>550384; 588931</t>
+          <t>549183; 586458</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>675625; 710697</t>
+          <t>675591; 711836</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>655517; 694984</t>
+          <t>655903; 696313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212570; 664289</t>
+          <t>489078; 525257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>550384; 588931</t>
+          <t>549183; 586458</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>675625; 710697</t>
+          <t>675591; 711836</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>655517; 694984</t>
+          <t>655903; 696313</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>212570; 664289</t>
+          <t>489078; 525257</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>716265</t>
+          <t>697987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>716265</t>
+          <t>697987</t>
         </is>
       </c>
     </row>
@@ -1776,42 +1776,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>801296; 852030</t>
+          <t>801712; 854916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>898447; 941685</t>
+          <t>899978; 942183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>901302; 942083</t>
+          <t>900009; 941514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>689422; 750536</t>
+          <t>673801; 722255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>801296; 852030</t>
+          <t>801712; 854916</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>898447; 941685</t>
+          <t>899978; 942183</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>901302; 942083</t>
+          <t>900009; 941514</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>689422; 750536</t>
+          <t>673801; 722255</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
     </row>
@@ -1924,42 +1924,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
     </row>
